--- a/Proyecto.xlsx
+++ b/Proyecto.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Nicolas\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\salacomputo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5E414F12-E7E3-43A9-B870-3FB3E3F2824B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AE28A3F-D66A-4177-AE74-5FD51BBF6983}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{41D4BEAF-8AA0-4F01-81A1-1E9FCECBF835}"/>
   </bookViews>
@@ -105,7 +105,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -573,15 +573,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{678D0DB0-44B3-4F9C-8544-1196D77FB440}">
   <dimension ref="A2:O10"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="93.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="93.375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="29" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.85546875" customWidth="1"/>
-    <col min="11" max="11" width="12.28515625" customWidth="1"/>
+    <col min="7" max="7" width="13.875" customWidth="1"/>
+    <col min="11" max="11" width="12.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15">
       <c r="F2" s="7" t="s">
         <v>20</v>
       </c>
@@ -613,7 +613,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" ht="15">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -660,7 +660,7 @@
         <v>46183</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" ht="15">
       <c r="A4" s="9" t="s">
         <v>14</v>
       </c>
@@ -679,7 +679,7 @@
       <c r="N4" s="6"/>
       <c r="O4" s="6"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:15">
       <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
@@ -687,7 +687,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="3">
-        <v>0.76</v>
+        <v>1</v>
       </c>
       <c r="D5" s="2">
         <v>46106</v>
@@ -706,7 +706,7 @@
       <c r="N5" s="6"/>
       <c r="O5" s="6"/>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:15">
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
@@ -714,7 +714,7 @@
         <v>4</v>
       </c>
       <c r="C6" s="3">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D6" s="2">
         <v>46120</v>
@@ -733,7 +733,7 @@
       <c r="N6" s="6"/>
       <c r="O6" s="6"/>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:15">
       <c r="A7" s="1" t="s">
         <v>18</v>
       </c>
@@ -741,7 +741,7 @@
         <v>4</v>
       </c>
       <c r="C7" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" s="2">
         <v>46155</v>
@@ -760,7 +760,7 @@
       <c r="N7" s="14"/>
       <c r="O7" s="14"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:15">
       <c r="A8" s="1" t="s">
         <v>19</v>
       </c>
@@ -768,7 +768,7 @@
         <v>4</v>
       </c>
       <c r="C8" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" s="2">
         <v>46169</v>
@@ -787,7 +787,7 @@
       <c r="N8" s="10"/>
       <c r="O8" s="6"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:15">
       <c r="F9" s="12"/>
       <c r="G9" s="12"/>
       <c r="H9" s="15"/>
@@ -797,7 +797,7 @@
       <c r="L9" s="15"/>
       <c r="M9" s="12"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:15">
       <c r="F10" s="12"/>
       <c r="H10" s="12"/>
       <c r="I10" s="12"/>
